--- a/Postulantes.xlsx
+++ b/Postulantes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documentos\Fino MAno\ASIGNAU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documentos\pruebacontundente\ASIGNAU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F2A5E5-647B-4FE9-8C63-6852079CD156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95AE911-5FB1-43F0-97A0-54D60385CA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{AEF26BAA-49D0-4461-A68C-25432696820F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="219">
   <si>
     <t xml:space="preserve">Reporte: </t>
   </si>
@@ -1448,6 +1448,15 @@
   </si>
   <si>
     <t>CONTRASEÑA</t>
+  </si>
+  <si>
+    <t>2026-1</t>
+  </si>
+  <si>
+    <t>30/03/2025</t>
+  </si>
+  <si>
+    <t>FISIOTERAPIA</t>
   </si>
 </sst>
 </file>
@@ -2077,20 +2086,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3828,11 +3837,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F14:G14"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="A10:G10"/>
@@ -3846,6 +3850,11 @@
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4258,6 +4267,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H9:H12"/>
@@ -4266,11 +4280,6 @@
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4431,10 +4440,10 @@
       <c r="E13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="97" t="s">
         <v>196</v>
       </c>
-      <c r="G13" s="99"/>
+      <c r="G13" s="98"/>
     </row>
     <row r="14" spans="1:8" s="21" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16">
@@ -4452,10 +4461,10 @@
       <c r="E14" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="99" t="s">
         <v>197</v>
       </c>
-      <c r="G14" s="101"/>
+      <c r="G14" s="100"/>
     </row>
     <row r="15" spans="1:8" s="37" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
@@ -4912,15 +4921,15 @@
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:23" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="97" t="s">
+      <c r="A38" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="97"/>
-      <c r="C38" s="97"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="97"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="101"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="F38" s="101"/>
+      <c r="G38" s="101"/>
       <c r="H38" s="45"/>
     </row>
     <row r="39" spans="1:23" s="64" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5033,15 +5042,15 @@
       <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:23" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="97" t="s">
+      <c r="A43" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="97"/>
-      <c r="C43" s="97"/>
-      <c r="D43" s="97"/>
-      <c r="E43" s="97"/>
-      <c r="F43" s="97"/>
-      <c r="G43" s="97"/>
+      <c r="B43" s="101"/>
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
       <c r="H43" s="45"/>
     </row>
     <row r="44" spans="1:23" s="64" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5189,12 +5198,16 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
@@ -5207,16 +5220,12 @@
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5618,19 +5627,19 @@
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="97" t="s">
+      <c r="A26" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="97"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
     </row>
     <row r="27" spans="1:11" s="71" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
@@ -5712,19 +5721,19 @@
       <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:11" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="97" t="s">
+      <c r="A32" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="97"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="97"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="97"/>
-      <c r="K32" s="97"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
     </row>
     <row r="33" spans="1:11" s="71" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A33" s="24" t="s">
@@ -5766,7 +5775,7 @@
         <v>194</v>
       </c>
       <c r="B34" s="41">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C34" s="18">
         <v>1718192021</v>
@@ -5801,7 +5810,7 @@
         <v>194</v>
       </c>
       <c r="B35" s="41">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C35" s="18">
         <v>1718192021</v>
@@ -5836,7 +5845,7 @@
         <v>194</v>
       </c>
       <c r="B36" s="41">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C36" s="18">
         <v>1718192021</v>
@@ -5871,7 +5880,7 @@
         <v>194</v>
       </c>
       <c r="B37" s="41">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C37" s="18">
         <v>1718192021</v>
@@ -5906,7 +5915,7 @@
         <v>194</v>
       </c>
       <c r="B38" s="41">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C38" s="18">
         <v>1718192021</v>
@@ -5941,7 +5950,7 @@
         <v>194</v>
       </c>
       <c r="B39" s="41">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C39" s="18">
         <v>1718192021</v>
@@ -5988,12 +5997,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="A26:K26"/>
@@ -6004,6 +6007,12 @@
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6012,258 +6021,300 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65785AA9-E5D5-4E09-BABB-24455D77952B}">
-  <dimension ref="A2:K9"/>
+  <dimension ref="A2:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="34.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625"/>
+    <col min="1" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="30.6640625" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" customWidth="1"/>
+    <col min="7" max="7" width="34.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="10" max="11" width="10.6640625"/>
+    <col min="12" max="12" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="D2" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="L2" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="K2" s="71"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="65">
+      <c r="M2" s="71"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" s="65">
+        <v>102</v>
+      </c>
+      <c r="C3" s="65">
         <v>1315848943</v>
       </c>
-      <c r="B3" s="65" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="75" t="s">
+      <c r="D3" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="67">
+      <c r="E3" s="67">
         <v>883.34</v>
       </c>
-      <c r="E3" s="65">
+      <c r="F3" s="65">
         <v>2</v>
-      </c>
-      <c r="F3" s="65">
-        <v>1</v>
       </c>
       <c r="G3" s="65">
         <v>1</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="65">
+        <v>1</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="J3" s="65">
+        <v>245111</v>
+      </c>
+      <c r="K3" s="65">
+        <v>349317</v>
+      </c>
+      <c r="L3" s="65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="65">
+        <v>102</v>
+      </c>
+      <c r="C4" s="65">
+        <v>1308489456</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="67">
+        <v>883.34</v>
+      </c>
+      <c r="F4" s="65">
+        <v>2</v>
+      </c>
+      <c r="G4" s="65">
+        <v>1</v>
+      </c>
+      <c r="H4" s="65">
+        <v>2</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="J4" s="65">
+        <v>228974</v>
+      </c>
+      <c r="K4" s="65">
+        <v>341425</v>
+      </c>
+      <c r="L4" s="65" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="65">
+        <v>102</v>
+      </c>
+      <c r="C5" s="65">
+        <v>1308489759</v>
+      </c>
+      <c r="D5" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="67">
+        <v>883.34</v>
+      </c>
+      <c r="F5" s="65">
+        <v>2</v>
+      </c>
+      <c r="G5" s="65">
+        <v>1</v>
+      </c>
+      <c r="H5" s="65">
+        <v>3</v>
+      </c>
+      <c r="I5" s="73" t="s">
+        <v>182</v>
+      </c>
+      <c r="J5" s="65">
+        <v>232605</v>
+      </c>
+      <c r="K5" s="65">
+        <v>341403</v>
+      </c>
+      <c r="L5" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="M5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="65">
+        <v>102</v>
+      </c>
+      <c r="C6" s="65">
+        <v>1309548031</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="67">
+        <v>883.34</v>
+      </c>
+      <c r="F6" s="65">
+        <v>1</v>
+      </c>
+      <c r="G6" s="65">
+        <v>2</v>
+      </c>
+      <c r="H6" s="65">
+        <v>1</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="I3" s="65">
+      <c r="J6" s="65">
         <v>227669</v>
       </c>
-      <c r="J3" s="65">
-        <v>341426</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="65">
-        <v>1308489456</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="D4" s="67">
+      <c r="K6" s="65">
+        <v>340487</v>
+      </c>
+      <c r="L6" s="65" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="65">
+        <v>102</v>
+      </c>
+      <c r="C7" s="65">
+        <v>1526894436</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="67">
         <v>883.34</v>
       </c>
-      <c r="E4" s="65">
-        <v>2</v>
-      </c>
-      <c r="F4" s="65">
+      <c r="F7" s="65">
         <v>1</v>
-      </c>
-      <c r="G4" s="65">
-        <v>2</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="I4" s="65">
-        <v>228974</v>
-      </c>
-      <c r="J4" s="65">
-        <v>341425</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="65">
-        <v>1308489759</v>
-      </c>
-      <c r="B5" s="65" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" s="75" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="67">
-        <v>883.34</v>
-      </c>
-      <c r="E5" s="65">
-        <v>2</v>
-      </c>
-      <c r="F5" s="65">
-        <v>1</v>
-      </c>
-      <c r="G5" s="65">
-        <v>3</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>182</v>
-      </c>
-      <c r="I5" s="65">
-        <v>232605</v>
-      </c>
-      <c r="J5" s="65">
-        <v>341403</v>
-      </c>
-      <c r="K5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="65">
-        <v>1309548031</v>
-      </c>
-      <c r="B6" s="65" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="67">
-        <v>883.34</v>
-      </c>
-      <c r="E6" s="65">
-        <v>1</v>
-      </c>
-      <c r="F6" s="65">
-        <v>2</v>
-      </c>
-      <c r="G6" s="65">
-        <v>1</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" s="65">
-        <v>227669</v>
-      </c>
-      <c r="J6" s="65">
-        <v>340487</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="65">
-        <v>1526894436</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="C7" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="67">
-        <v>883.34</v>
-      </c>
-      <c r="E7" s="65">
-        <v>1</v>
-      </c>
-      <c r="F7" s="65">
-        <v>2</v>
       </c>
       <c r="G7" s="65">
         <v>2</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="65">
+        <v>2</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="I7" s="65">
+      <c r="J7" s="65">
         <v>228974</v>
       </c>
-      <c r="J7" s="65">
+      <c r="K7" s="65">
         <v>340486</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="65">
+      <c r="L7" s="65" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" s="65">
+        <v>102</v>
+      </c>
+      <c r="C8" s="65">
         <v>1113265978</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="D8" s="75" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="67">
+        <v>883.34</v>
+      </c>
+      <c r="F8" s="65">
+        <v>1</v>
+      </c>
+      <c r="G8" s="65">
+        <v>2</v>
+      </c>
+      <c r="H8" s="65">
+        <v>3</v>
+      </c>
+      <c r="I8" s="73" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" s="65">
+        <v>232605</v>
+      </c>
+      <c r="K8" s="65">
+        <v>340464</v>
+      </c>
+      <c r="L8" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="67">
-        <v>883.34</v>
-      </c>
-      <c r="E8" s="65">
-        <v>1</v>
-      </c>
-      <c r="F8" s="65">
-        <v>2</v>
-      </c>
-      <c r="G8" s="65">
-        <v>3</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>182</v>
-      </c>
-      <c r="I8" s="65">
-        <v>232605</v>
-      </c>
-      <c r="J8" s="65">
-        <v>340464</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="56"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="56"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D9" s="71"/>
+      <c r="E9" s="30"/>
       <c r="F9" s="56"/>
       <c r="G9" s="56"/>
       <c r="H9" s="56"/>
       <c r="I9" s="56"/>
       <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
